--- a/reports/20260507/API_role_expiry_claude.xlsx
+++ b/reports/20260507/API_role_expiry_claude.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Create role 'AutoRoleExp_efea4f_01' with DefaultExpiryInDays=30.</t>
+          <t>Create role 'AutoRoleExp_5f1eb1_01' with DefaultExpiryInDays=30.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>RoleId=375, name=AutoRoleExp_efea4f_01, days=30</t>
+          <t>RoleId=395, name=AutoRoleExp_5f1eb1_01, days=30</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>userId=455, expected~=2026-06-06 11:46:29, stored=2026-06-06 11:46:30</t>
+          <t>userId=481, expected~=2026-06-06 18:38:51, stored=2026-06-06 18:38:54</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>userId=455, roleId=375, expiryOn=2026-06-06T11:46:30</t>
+          <t>userId=481, roleId=395, expiryOn=2026-06-06T18:38:54</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>userId=459, roleId=379, expiry_on=None (expected null)</t>
+          <t>userId=483, roleId=399, expiry_on=None (expected null)</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>days=10, userId=461, expected~=2026-05-17 11:46:37, stored=2026-05-17 11:46:45</t>
+          <t>days=10, userId=487, expected~=2026-05-17 18:39:12, stored=2026-05-17 18:39:15</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>message='Refreshed successfully.', old=2026-06-06T11:46:30, new~=2026-06-06 11:46:48, expected~=2026-06-06 11:46:47</t>
+          <t>message='Refreshed successfully.', old=2026-06-06T18:38:54, new~=2026-06-06 18:39:21, expected~=2026-06-06 18:39:21</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>role_days=15, new~=2026-05-22 11:46:50, expected~=2026-05-22 11:46:49</t>
+          <t>role_days=15, new~=2026-05-22 18:39:23, expected~=2026-05-22 18:39:22</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>roleId=375, records=1 (expected 1)</t>
+          <t>roleId=395, records=1 (expected 1)</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200, role created (id=389) — accepted negative value</t>
+          <t>HTTP 200, role created (id=409) — accepted negative value</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200, role created (id=391), user expiry_on=None</t>
+          <t>HTTP 200, role created (id=411), user expiry_on=None</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>HTTP 200, role created (id=393) — large value accepted</t>
+          <t>HTTP 200, role created (id=413) — large value accepted</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>SQL: HTTP 200, rejected | XSS: HTTP 403 | SQL_UNION: HTTP 200, rejected</t>
+          <t>SQL: HTTP 200, rejected | XSS: HTTP 200, rejected | SQL_UNION: HTTP 200, rejected</t>
         </is>
       </c>
     </row>
